--- a/outputs/54085.xlsx
+++ b/outputs/54085.xlsx
@@ -1,93 +1,90 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27531"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97342\Desktop\130_excel公式已检查\54085\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FA512DD-FB96-444F-AE71-C6A6EA9DE0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11949" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
-  <si>
-    <t xml:space="preserve">Item</t>
-  </si>
-  <si>
-    <t xml:space="preserve">List of Items</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desired Result</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pears</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apples</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oranges</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bananas</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>List of Items</t>
+  </si>
+  <si>
+    <t>Desired Result</t>
+  </si>
+  <si>
+    <t>Pears</t>
+  </si>
+  <si>
+    <t>Apples</t>
+  </si>
+  <si>
+    <t>Oranges</t>
+  </si>
+  <si>
+    <t>Bananas</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
       <sz val="18"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <u val="single"/>
+      <b/>
+      <u/>
       <sz val="18"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
-      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -99,106 +96,93 @@
     </fill>
   </fills>
   <borders count="4">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="medium"/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="mediumDashDot"/>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="mediumDashDot">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="medium"/>
-      <right style="medium"/>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="medium"/>
-      <right style="medium"/>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
       <top/>
-      <bottom style="medium"/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -233,55 +217,119 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
                 <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
                 <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
                 <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
                 <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
                 <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
@@ -289,24 +337,33 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
                 <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
@@ -319,7 +376,13 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -329,13 +392,15 @@
         <a:solidFill>
           <a:schemeClr val="phClr">
             <a:tint val="95000"/>
+            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
+                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
               </a:schemeClr>
@@ -343,6 +408,7 @@
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
+                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
               </a:schemeClr>
@@ -350,34 +416,33 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.87109375" defaultRowHeight="21.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="22.3" x14ac:dyDescent="0.5"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22.13"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="5" style="1" width="8.87"/>
+    <col min="1" max="1" width="22.1875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.3125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.125" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:3" ht="34.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -388,49 +453,37 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="4" t="str">
-        <f aca="false" t="array" ref="C2:C2">IFERROR(INDEX($B$2:$B$5,SMALL(IF($B$2:$B$5&lt;&gt;$A$2,ROW($B$2:$B$5)-1),ROW()-1)),"")</f>
-        <v>Apples</v>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.5">
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4" t="str">
-        <f aca="false" t="array" ref="C3:C3">IFERROR(INDEX($B$2:$B$5,SMALL(IF($B$2:$B$5&lt;&gt;$A$2,ROW($B$2:$B$5)-1),ROW()-1)),"")</f>
-        <v>Oranges</v>
-      </c>
+      <c r="C3" s="4"/>
     </row>
-    <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.5">
       <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="4" t="str">
-        <f aca="false" t="array" ref="C4:C4">IFERROR(INDEX($B$2:$B$5,SMALL(IF($B$2:$B$5&lt;&gt;$A$2,ROW($B$2:$B$5)-1),ROW()-1)),"")</f>
-        <v>Bananas</v>
-      </c>
+      <c r="C4" s="4"/>
     </row>
-    <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.5">
       <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="5"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>